--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy</t>
+    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -565,7 +565,7 @@
 ・Seriesの階層の(0008,0060)を集約する、または(0008,0060)　と　(0008, 0061) のOR。但し、重複する値は1つにまとめて表現。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>.code</t>
@@ -580,7 +580,7 @@
     <t>ImagingStudy.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|Group)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -611,7 +611,7 @@
     <t>ImagingStudy.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -673,7 +673,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
 </t>
   </si>
   <si>
@@ -709,7 +709,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -825,7 +825,7 @@
     <t>ImagingStudy.procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -881,7 +881,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -932,7 +932,7 @@
     <t>研究の理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -950,7 +950,7 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|Media|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|Media|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1227,7 +1227,7 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1252,7 +1252,7 @@
     <t>DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの左右コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality</t>
+    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality|4.0.1</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1261,7 +1261,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1353,13 +1353,13 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1447,7 +1447,7 @@
     <t>【JP Core仕様】SOPクラスUID。DICOMタグマッピングにある値をそのまま設定。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes</t>
+    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes|0.1.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>
@@ -1827,7 +1827,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="220.078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1842,7 +1842,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="114.3125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.2265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -565,7 +565,7 @@
 ・Seriesの階層の(0008,0060)を集約する、または(0008,0060)　と　(0008, 0061) のOR。但し、重複する値は1つにまとめて表現。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>.code</t>
@@ -580,7 +580,7 @@
     <t>ImagingStudy.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|Group|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|Group)
 </t>
   </si>
   <si>
@@ -611,7 +611,7 @@
     <t>ImagingStudy.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -673,7 +673,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
 </t>
   </si>
   <si>
@@ -709,7 +709,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -825,7 +825,7 @@
     <t>ImagingStudy.procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
 </t>
   </si>
   <si>
@@ -881,7 +881,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -932,7 +932,7 @@
     <t>研究の理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -950,7 +950,7 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|Media|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|Media|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|DocumentReference)
 </t>
   </si>
   <si>
@@ -1227,7 +1227,7 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1252,7 +1252,7 @@
     <t>DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの左右コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1261,7 +1261,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1353,13 +1353,13 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|Device|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Device|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1447,7 +1447,7 @@
     <t>【JP Core仕様】SOPクラスUID。DICOMタグマッピングにある値をそのまま設定。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes|0.1.0</t>
+    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>
@@ -1827,7 +1827,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="220.078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1842,7 +1842,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="114.3125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
